--- a/backend/data/financials_by_company/000012.SZ.xlsx
+++ b/backend/data/financials_by_company/000012.SZ.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cashflow" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="income" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cashflow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,6 +420,1013 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:BC6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tax Effect Of Unusual Items</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tax Rate For Calcs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Normalized EBITDA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total Unusual Items</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Total Unusual Items Excluding Goodwill</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing Operation Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Reconciled Depreciation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Reconciled Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Net Interest Income</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Interest Expense</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Normalized Income</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing And Discontinued Operation</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Rent Expense Supplemental</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Total Operating Income As Reported</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Diluted Average Shares</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Basic Average Shares</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Diluted EPS</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Basic EPS</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Net Income Common Stockholders</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Otherunder Preferred Stock Dividend</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Minority Interests</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Net Income Including Noncontrolling Interests</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Net Income Continuous Operations</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Tax Provision</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Pretax Income</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Other Non Operating Income Expenses</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Special Income Charges</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Other Special Charges</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Write Off</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Impairment Of Capital Assets</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Net Non Operating Interest Income Expense</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Total Other Finance Cost</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Interest Expense Non Operating</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Interest Income Non Operating</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Operating Expense</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Other Operating Expenses</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Depreciation And Amortization In Income Statement</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Depreciation Income Statement</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Research And Development</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Selling General And Administration</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Selling And Marketing Expense</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>General And Administrative Expense</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Rent And Landing Fees</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-45876547.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1896589933</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-183506190</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-183506190</v>
+      </c>
+      <c r="G2" t="n">
+        <v>125668291</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1366877826</v>
+      </c>
+      <c r="I2" t="n">
+        <v>11714880100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1713083743</v>
+      </c>
+      <c r="K2" t="n">
+        <v>346205917</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-216147397</v>
+      </c>
+      <c r="M2" t="n">
+        <v>247130850</v>
+      </c>
+      <c r="N2" t="n">
+        <v>40278639</v>
+      </c>
+      <c r="O2" t="n">
+        <v>263297933.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>125668291</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>13245939293</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8208876</v>
+      </c>
+      <c r="S2" t="n">
+        <v>52178494</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3141707275</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3141707275</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>125668291</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>125668291</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>20334152</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>105334139</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>105334139</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-6259072</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>99075067</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>46896573</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-183506190</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-19981685</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-52872082</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>256359957</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-216147397</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>9295186</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>247130850</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>40278639</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>473029715</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1531059193</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>146502109</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>178987258</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>178987258</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>519332680</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>211573099</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>77697182</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>133875917</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8208876</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2004088908</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>11714880100</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>13718969008</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>13718969008</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-76620907.27429</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.148867</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2365601526</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-514694648</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-514694648</v>
+      </c>
+      <c r="G3" t="n">
+        <v>266772318</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1319611112</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12848639959</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1850906878</v>
+      </c>
+      <c r="K3" t="n">
+        <v>531295766</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-192817252</v>
+      </c>
+      <c r="M3" t="n">
+        <v>240388865</v>
+      </c>
+      <c r="N3" t="n">
+        <v>55326006</v>
+      </c>
+      <c r="O3" t="n">
+        <v>704846058.72571</v>
+      </c>
+      <c r="P3" t="n">
+        <v>266772318</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>14456685116</v>
+      </c>
+      <c r="R3" t="n">
+        <v>10997676</v>
+      </c>
+      <c r="S3" t="n">
+        <v>297946076</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2964136867</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2964136867</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X3" t="n">
+        <v>266772318</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>266772318</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>19171775</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>247600543</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>247600543</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>43306358</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>290906901</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-7039175</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-514694648</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-42232656</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-24154920</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>581082224</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-192817252</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>7754393</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>240388865</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>55326006</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>998701285</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1608045157</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>137971275</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>209095206</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>209095206</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>611497261</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>205499724</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>60261934</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>145237790</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10997676</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2606746442</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>12848639959</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>15455386401</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>15455386401</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-19376613.657173</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.052543</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3478094771</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-368774882</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-368774882</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1655614446</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1248964318</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14149865508</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3109319889</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1860355571</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-159756745</v>
+      </c>
+      <c r="M4" t="n">
+        <v>228159638</v>
+      </c>
+      <c r="N4" t="n">
+        <v>72612051</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2005012714.342827</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1655614446</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>16038227116</v>
+      </c>
+      <c r="R4" t="n">
+        <v>13816208</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1622425421</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3065952678</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3065952678</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1655614446</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1655614446</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>109179316</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1546435130</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1546435130</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>85760803</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1632195933</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>9770512</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-368774882</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>551072</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>21486353</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>346737457</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-159756745</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4209158</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>228159638</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>72612051</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2156637250</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1888361608</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>149584802</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>189979394</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>189979394</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>739301765</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>263384913</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>92486669</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>170898244</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>13816208</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4044998858</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>14149865508</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>18194864366</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>18194864366</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-19434245.565227</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.103335</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3678985806</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-188070138</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-188070138</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2037202500</v>
+      </c>
+      <c r="H5" t="n">
+        <v>999316458</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11006795373</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3490915668</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2491599210</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-144746283</v>
+      </c>
+      <c r="M5" t="n">
+        <v>212724263</v>
+      </c>
+      <c r="N5" t="n">
+        <v>71751429</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2205838392.434773</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2037202500</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12630741879</v>
+      </c>
+      <c r="R5" t="n">
+        <v>9418713</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2263249853</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3086670455</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3086670455</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2037202500</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2037202500</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-6184688</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2043387188</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2043387188</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>235487759</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2278874947</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>15625094</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-188070138</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-15213059</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>47720107</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>155563090</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-144746283</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3773449</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>212724263</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>71751429</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2567965119</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1623946506</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>135473792</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>114878297</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>114878297</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>644146614</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>244770769</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>77285636</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>167485133</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9418713</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4191911625</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11006795373</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>15198706998</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>15198706998</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>60490281</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:BT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1714,7 +2722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2537,13 +3545,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EW2"/>
+  <dimension ref="A1:EY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2984,330 +3992,340 @@
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
+          <t>recommendationMean</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>numberOfAnalystOpinions</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3329,10 +4347,8 @@
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>518067</t>
-        </is>
+      <c r="D2" t="n">
+        <v>518067</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3409,34 +4425,34 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>4.38</v>
+        <v>4.31</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>4.34</v>
       </c>
       <c r="W2" t="n">
-        <v>4.01</v>
+        <v>4.23</v>
       </c>
       <c r="X2" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.38</v>
+        <v>4.31</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>4.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.01</v>
+        <v>4.23</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="AC2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="n">
         <v>1753228800</v>
@@ -3448,36 +4464,34 @@
         <v>2.68</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Infinity</t>
-        </is>
+        <v>0.352</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>440.00003</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7.941177</v>
+        <v>8.627451000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>90549239</v>
+        <v>68624961</v>
       </c>
       <c r="AL2" t="n">
-        <v>90549239</v>
+        <v>68624961</v>
       </c>
       <c r="AM2" t="n">
-        <v>38114485</v>
+        <v>40598363</v>
       </c>
       <c r="AN2" t="n">
-        <v>88616466</v>
+        <v>89243259</v>
       </c>
       <c r="AO2" t="n">
-        <v>88616466</v>
+        <v>89243259</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.03</v>
+        <v>4.38</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.04</v>
+        <v>4.39</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -3486,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>12321999872</v>
+        <v>13386863616</v>
       </c>
       <c r="AU2" t="n">
-        <v>9197002592</v>
+        <v>9898127068</v>
       </c>
       <c r="AV2" t="n">
         <v>3.62</v>
@@ -3504,19 +4518,19 @@
         <v>0.374026</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.90334654</v>
+        <v>0.9814135</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2744</v>
+        <v>4.2402</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5827</v>
+        <v>4.5644</v>
       </c>
       <c r="BC2" t="n">
         <v>0.02</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.00456621</v>
+        <v>0.004640371</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -3527,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>20128303104</v>
+        <v>20905607168</v>
       </c>
       <c r="BH2" t="n">
         <v>0.00082</v>
@@ -3551,7 +4565,7 @@
         <v>4.36</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.9288991</v>
+        <v>1.0091743</v>
       </c>
       <c r="BP2" t="n">
         <v>1767139200</v>
@@ -3566,7 +4580,7 @@
         <v>11155333</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BU2" t="n">
         <v>0.51</v>
@@ -3580,16 +4594,16 @@
         <v>1561507200</v>
       </c>
       <c r="BX2" t="n">
-        <v>1.476</v>
+        <v>1.533</v>
       </c>
       <c r="BY2" t="n">
-        <v>13.415</v>
+        <v>13.933</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.12903225</v>
+        <v>-0.07708782</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.27697718</v>
+        <v>0.22635591</v>
       </c>
       <c r="CB2" t="n">
         <v>0.07000000000000001</v>
@@ -3603,256 +4617,264 @@
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="CF2" t="n">
         <v>6.3</v>
       </c>
       <c r="CG2" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="CH2" t="n">
-        <v>6.3</v>
+        <v>5.75</v>
       </c>
       <c r="CI2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CK2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="CJ2" t="n">
         <v>1</v>
       </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>strong_buy</t>
+        </is>
+      </c>
       <c r="CL2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM2" t="n">
         <v>3282547456</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>1.098</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>1500438912</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>10898492416</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
         <v>0.676</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>1.002</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CS2" t="n">
         <v>13640390656</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CT2" t="n">
         <v>81.099</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
         <v>4.303</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="n">
         <v>0.0025499999</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CW2" t="n">
         <v>-0.00053</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CX2" t="n">
         <v>1838163200</v>
       </c>
-      <c r="CX2" t="n">
+      <c r="CY2" t="n">
         <v>497287616</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="CZ2" t="n">
         <v>1116372608</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DA2" t="n">
         <v>-0.026</v>
       </c>
-      <c r="DA2" t="n">
+      <c r="DB2" t="n">
         <v>0.13475999</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DC2" t="n">
         <v>0.11</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DD2" t="n">
         <v>-0.02545</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>000012.SZ</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DJ2" t="b">
+      <c r="DK2" t="b">
         <v>0</v>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>POSTPOST</t>
+        </is>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>694747800000</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.09000015</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>4.23 - 4.41</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>40598363</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.7800002</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.21546967</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>3.62 - 5.27</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.8699999</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.16508538</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-7.708782</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1650884340</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1650974400</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>finmb_878683</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>CSG HOLDING CO</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
         <is>
           <t>CSG Holding Co., Ltd.</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>1780038243</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-7.5342445</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="EM2" t="n">
+        <v>0.15980005</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0.037686914</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-0.1644001</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-0.0360179</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>1.0 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="ET2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>1780988649</v>
+      </c>
+      <c r="EV2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>finmb_878683</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>CSG HOLDING CO</t>
-        </is>
-      </c>
-      <c r="EA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>694747800000</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.32999992</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>4.01 - 4.43</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>38114485</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.4300003</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.11878462</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>3.62 - 5.27</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-1.2199998</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.23149902</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-12.903225</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1650884340</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>1650974400</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.22440004</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-0.052498605</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>-0.5326996000000001</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-0.11624143</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EW2" t="inlineStr"/>
+      <c r="EW2" t="n">
+        <v>2.0881708</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="EY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
